--- a/мониторинг БШО.xlsx
+++ b/мониторинг БШО.xlsx
@@ -52,6 +52,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="матем." sheetId="44" state="visible" r:id="rId44"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="литер." sheetId="45" state="visible" r:id="rId45"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="инфор-ка" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=" биология" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames>
     <definedName name="Z_C96CBF95_39C2_41AB_8666_CD7F764B518E_.wvu.FilterData" localSheetId="15" hidden="1">'7А'!$A$1:$N$35</definedName>
@@ -12626,7 +12627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.85546875" customWidth="1" style="236" min="1" max="1"/>
@@ -13591,7 +13592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.28515625" customWidth="1" style="236" min="1" max="1"/>
@@ -15565,7 +15566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.7109375" customWidth="1" style="236" min="1" max="1"/>
@@ -16733,7 +16734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.28515625" customWidth="1" style="236" min="1" max="1"/>
@@ -17914,7 +17915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.85546875" customWidth="1" style="236" min="1" max="1"/>
@@ -18854,7 +18855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.28515625" customWidth="1" style="236" min="1" max="1"/>
@@ -20326,7 +20327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="236" min="1" max="1"/>
@@ -22015,7 +22016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.5703125" customWidth="1" style="236" min="1" max="1"/>
@@ -22994,7 +22995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.140625" customWidth="1" style="236" min="1" max="1"/>
@@ -23886,7 +23887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="4.85546875" customWidth="1" style="236" min="1" max="1"/>
@@ -35814,7 +35815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36074,7 +36075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36335,7 +36336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.85546875" customWidth="1" style="236" min="1" max="1"/>
@@ -37178,7 +37179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB99"/>
+  <dimension ref="A1:CU99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.85546875" customWidth="1" style="236" min="1" max="1"/>
@@ -78414,6 +78415,172 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>8Б</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Фамилия</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Имя</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Отчество</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Класс</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Байрышева</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Юлия</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Викторовна</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7В</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ветер</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Алиса</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Евгеньевна</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7В</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Гиб</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Денис</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Альбертович</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7В</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Колесова</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Елизавета</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Игоревна</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7В</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Южикова</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Полина</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Игоревна</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7В</t>
         </is>
       </c>
     </row>
